--- a/football_promotion_relegation_top5.xlsx
+++ b/football_promotion_relegation_top5.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P&amp;R Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Churn Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Notes &amp; Methodology" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Promotion &amp; Relegation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,6 +37,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="8">
@@ -105,68 +107,74 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -533,22 +541,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Promotion &amp; Relegation - Top 5 European Football Pyramids, Tiers 1-5 (2024-25 / 2025-26)</t>
@@ -573,12 +581,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Clubs in division</t>
+          <t>Clubs</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Promoted / season (auto + playoff)</t>
+          <t>Clubs promoted</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -588,7 +596,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Relegated / season (auto + playoff)</t>
+          <t>Clubs relegated</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,12 +606,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Notes (playoffs, conditional P/R, reserve-team &amp; regional-group rules)</t>
+          <t>Has playoff?</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Official source</t>
         </is>
       </c>
     </row>
@@ -621,14 +629,14 @@
       <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>— (top tier)</t>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -636,9 +644,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>3 (3 auto + 0 PO)</t>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -646,14 +654,14 @@
           <t>15.0%</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>No relegation play-off; bottom 3 down. No reserve/B-teams anywhere in the pyramid.</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 Premier League</t>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>premierleague.com</t>
         </is>
       </c>
     </row>
@@ -671,14 +679,14 @@
       <c r="C4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -686,9 +694,9 @@
           <t>12.5%</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>3 (3 auto + 0 PO)</t>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -696,14 +704,14 @@
           <t>12.5%</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>PO contested by 3rd-6th, 1 promoted (Wembley final). From 2026-27 the PO expands to 3rd-8th (6 clubs), still 1 promoted. No reserve teams in EFL.</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 EFL Championship; EFL Championship play-offs (Wikipedia)</t>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>efl.com</t>
         </is>
       </c>
     </row>
@@ -721,14 +729,14 @@
       <c r="C5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -736,9 +744,9 @@
           <t>12.5%</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>4 (4 auto + 0 PO)</t>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -746,14 +754,14 @@
           <t>16.7%</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>PO contested by 3rd-6th, 1 promoted.</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 EFL League One</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>efl.com</t>
         </is>
       </c>
     </row>
@@ -771,14 +779,14 @@
       <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>4 (3 auto + 1 PO)</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -786,9 +794,9 @@
           <t>16.7%</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2 (2 auto + 0 PO)</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -796,14 +804,14 @@
           <t>8.3%</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>PO contested by 4th-7th, 1 promoted. Lowest fully-professional tier.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 EFL League Two</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>efl.com</t>
         </is>
       </c>
     </row>
@@ -815,20 +823,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>National League (Premier)</t>
+          <t>National League</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2 (1 auto + 1 PO)</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -836,9 +844,9 @@
           <t>8.3%</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>~4 (4 auto + 0 PO)</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -846,1328 +854,1080 @@
           <t>16.7%</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>PO contested by 2nd-7th (6 clubs), 1 promoted. Promotion to EFL is CONDITIONAL on ground-grading (EFL Cat. A, min 4,000 capacity); a champion failing it can be denied. Tier 6 below (NL North/South) is regionalized; tier 5 itself is national. Relegation normally 4 but FA can adjust if an EFL club is expelled. No reserve/B-teams permitted.</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 National League; National League (English football) (Wikipedia); FA National League System regs &amp; ground-grading handbook</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>thenationalleague.org.uk</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>LaLiga (EA Sports)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>— (top tier)</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>3 (3 auto + 0 PO)</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>No relegation play-off. Reserve teams (filiales) can NEVER reach this tier.</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 La Liga</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>laliga.com</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>LaLiga2 (Hypermotion)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>13.6%</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>4 (4 auto + 0 PO)</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>18.2%</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>PO contested by 3rd-6th, 1 promoted. CEILING for all B-teams: a B-team in the top 6 cannot be promoted; the slot reroutes to the next eligible club.</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 Segunda Division</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>laliga.com</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Primera Federacion</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>40 (2 groups x 20)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>4 (2 auto + 2 PO)</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>10.0%</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>10 (10 auto + 0 PO)</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Per group: 1 champion auto + 1 PO winner (from 2nd-5th). Per-group promotion 10%, relegation 25% (bottom 5 of each group). RFEF-run; B-team rule applies (ineligible berths reroute).</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 Primera Federacion; 2024 Primera Federacion play-offs</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>rfef.es</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Segunda Federacion</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>90 (5 groups x 18)</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>10 (5 auto + 5 PO)</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>11.1%</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>~27 (25 auto + ~2 PO)</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>~27</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>~30%</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Per group: 1 champion auto + 1 PO winner (2nd-5th). Relegation = 5 auto/group + ~2 via a NATIONAL mini-playoff among the weakest 13th-placed sides, so totals vary. B-team rule applies.</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 Segunda Federacion; 2024 Segunda Federacion play-offs</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Yes (promotion + relegation)</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>rfef.es</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Tercera Federacion</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>~325 (18 regional groups)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>27 (18 auto + 9 PO)</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>~325 (18 groups)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>~8.3%</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>~54+ (regionally set)</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>~17%+</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>18 group champions auto + 9 via play-offs (2nd-5th). The 9 PO places do not divide evenly per group (per-group figures are averages). Relegation count is set INDEPENDENTLY by each autonomous-community federation (~3-5/group) and varies by group and year. B-team rule applies.</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 Tercera Federacion; Spanish football league system (Wikipedia)</t>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>~54+</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>~17%</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>rfef.es</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>— (top tier)</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Relegation play-off (Relegation): 16th vs 2. Bundesliga 3rd, two legs, no away goals since 2021-22. Auto alone = 11.1%; with PO loss = 16.7%.</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Bundesliga.com (official) P/R FAQ; DFL.de 2025 relegation play-off schedule</t>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>Yes (relegation)</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>bundesliga.com</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>2. Bundesliga</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Two play-offs touch this tier: up (3rd vs BL 16th) and down (16th vs 3. Liga 3rd). Highest tier a reserve ('II') team CANNOT reach.</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Wikipedia 2. Bundesliga; Bundesliga.com</t>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>Yes (promotion + relegation)</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>bundesliga.com</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>3. Liga</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>10.0-15.0%</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>4 (4 auto + 0 PO)</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>PO: 3rd vs 2. Bundesliga 16th. Reserve ('II') teams may PLAY here but CANNOT be promoted (slot passes to next eligible club); reserves also barred from DFB-Pokal. Single national league (DFB-run).</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 3. Liga; Reserve team (Wikipedia)</t>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>dfb.de</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Regionalliga</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>~90 (5 groups x 18)</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>~4 of 5 champions (~3 direct + 1 PO)</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>~4.4% (national)</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>varies (~2-4 / group)</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>~10-20% / group</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>ANOMALY: 5 regional champions (Nord, Nordost, West, Sudwest, Bayern) but only ~4 promotion slots, so ONE champion misses out each year. Sudwest &amp; West usually direct; 3rd direct slot rotates; the other two contest a play-off. 2024-25: Sudwest/West/Bayern direct, Nord-Nordost PO. 4-division reform approved in principle (earliest 2028-29). Reserve teams cannot be promoted.</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 Regionalliga; Promotion to the 3. Liga (Wikipedia); World Football Index</t>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>~4</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>~4.4%</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>~10-20%</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Yes (promotion)</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>dfb.de</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Oberliga</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>varies (14 parallel leagues, ~16-18 each)</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>~1 champion / league (some via PO)</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>~6% / league</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>varies (regional)</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>varies (14 leagues)</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>~1/league</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>~6%</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Run by state associations, so club counts and P/R numbers are set annually by each region's promotion/relegation key. Same reserve-team promotion bar applies.</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 Oberliga; Oberliga (football) (Wikipedia)</t>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>Sometimes (regional)</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>dfb.de</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>— (top tier)</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>3 (3 auto + 0 PO)</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>Cleanest tier; no playout. Reserve teams barred from Serie A.</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia 2025-26 Serie A; Serie A (Wikipedia)</t>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>legaseriea.it</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Serie B</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>3 (2 auto + 1 PO)</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>4 (3 auto + 1 playout)</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>PO contested by 3rd-8th, 1 promoted. PLAYOUT (16th v 17th) decides the 4th relegation, but is CANCELLED if 16th finishes &gt;=4 pts clear (17th relegated automatically).</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 Serie B; Football-Italia (playout); Destination Calcio</t>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>Yes (promotion + relegation)</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>legab.it</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Serie C</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>60 (3 groups x 20)</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>4 (3 auto + 1 large PO)</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>6.7%</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>~9 (3 auto + ~6 playout)</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>~9</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>~15%</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>3 group champions auto + ONE promotion from a ~28-team national play-off bracket (lowest yield-per-participant anywhere). Relegation = 1 auto/group + playouts. Reserve/U23 teams allowed (Juventus Next Gen 2018, Atalanta U23 2023). Heavy ripescaggio (see workbook 'Cross-cutting notes').</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 Serie C; nss-sports; Cult of Calcio; Juventus Next Gen (Wikipedia)</t>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>Yes (promotion + relegation)</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>legapro.it</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Serie D</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>~162 (9 groups x ~18)</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>9 (9 auto + 0 PO)</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>~162 (9 groups x 18)</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>~5.6%</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>~36 (~9 auto + ~27 playout)</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>~36</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>~22%</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>9 group champions promoted automatically (runner-up play-offs only set ripescaggio priority). Top amateur tier (LND). Mid-season withdrawals/exclusions reshuffle relegation math.</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 Serie D</t>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>Yes (relegation)</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>lnd.it</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Eccellenza</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>~474 (~28 regional groups)</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>~36 (~28 champions + ~7 PO + 1 cup)</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>~474 (~28 groups)</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>~36</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>~7.6%</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>region-set (~2-4 / group)</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>~2-4/group</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>~12-20%</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>Fully regionalized: each regional committee sets its own group sizes, play-off bracket and relegation count. Coppa Italia Dilettanti winner also promoted. Reserve teams permitted.</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia Eccellenza; Italian football league system</t>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>Yes (promotion + relegation)</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>lnd.it</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Ligue 1 (McDonald's)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>— (top tier)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>2 auto + 1 barrage (16th)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>18 clubs since 2023-24. Barrage: 16th vs Ligue 2 PO winner (2 legs). DNCG (financial regulator) can administratively relegate clubs regardless of position (e.g. Lyon provisionally relegated 2025, reinstated on appeal).</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>Wikipedia 2024-25 &amp; 2025-26 Ligue 1; Ligue 1 relegation/promotion play-offs; ESPN (Lyon); DNCG (Wikipedia)</t>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>Yes (relegation barrage)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>lfp.fr</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Ligue 2</t>
         </is>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>2 auto + 1 barrage</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>2 auto + 1 barrage</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>PO winner (~3rd-5th) plays Ligue 1 16th; relegation barrage 16th vs National 3rd (reintroduced 2024-25 with the 20-&gt;18 downsizing). DNCG can force relegation (Bordeaux dropped two tiers to National 2 in 2024-25).</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>Wikipedia Ligue 2; 2024-25 &amp; 2025-26 Ligue 2; France 3 (Bordeaux DNCG)</t>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>Yes (promotion + relegation barrage)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>lfp.fr</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Championnat National</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>2 auto + 1 barrage</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>11.1-16.7%</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>2 (auto, transitional)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>~11.1%</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>3rd plays Ligue 2 16th in the barrage. Relegation reduced to ~2 during downsizing (historically 3-4). Becomes professional 'Ligue 3' from 2026-27.</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>Wikipedia Championnat National; 2024-25 Championnat National; FFF official Ligue 3 launch</t>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Yes (promotion barrage)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>fff.fr</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Championnat National 2</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>National 2</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>48 (3 groups x 16)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>up to 3 (group champions)*</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>~6.25%</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>~10 in 2024-25 (restructuring)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>~10</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>~20.8%</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>*3 regional groups (not 4). Reserve teams may WIN a group but CANNOT be promoted to National (tier 3); the slot reroutes to the next eligible club. Geographic groups -&gt; relegation counts vary by group. Renamed 'National 1' from 2026-27.</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>Wikipedia Championnat National 2; 2024-25 Championnat National 2; FFF N1/N2 regs</t>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>fff.fr</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Championnat National 3</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="n">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>National 3</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>140 -&gt; 112 (10 -&gt; 8 groups x 14)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>1 per group (10 -&gt; 8)*</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>~7.1% / group</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>many (variable, regional)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>variable / elevated</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>*Run by the regional leagues; mid-downsizing (140-&gt;112) temporarily inflates relegation. Group winner promoted (next eligible if ineligible). Reserve teams capped at tier 4. Renamed 'National 2' from 2026-27.</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>Wikipedia Championnat National 3; 2024-25 Championnat National 3; French football league system</t>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>140 (10 groups x 14)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>~7.1%</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>fff.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Note: Structure as of the 2024-25 / 2025-26 seasons. 'Clubs promoted/relegated' are totals per season including any playoff places; % = clubs moved / clubs in division x 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Note: Ranges are given where the count depends on a playoff/barrage, financial licensing, reserve-team eligibility, or ongoing league restructuring (mainly the regionalised lower tiers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Note: 'Has playoff?' covers promotion/relegation playoffs (England playoffs, German Relegation, Italian playout, French barrage). Regionalised tiers' relegation counts are set annually by regional federations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Note: Sources are the official governing-body / league websites (Premier League, EFL &amp; National League; LaLiga &amp; RFEF; Bundesliga &amp; DFB; Lega Serie A/B, Lega Pro &amp; LND; LFP &amp; FFF).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A29:J29"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Where promotion/relegation churn is highest and lowest</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Highest churn</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Lowest churn</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Promotion % (share moving up)</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>England League Two 16.7%; Italy Serie B 15%; Eng Championship/League One 12.5%</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Germany Regionalliga ~4.4% (national); Italy Serie D ~5.6% / Serie C 6.7%; Eng National League 8.3%</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>Upper-mid professional tiers move the most clubs up relative to size; vast regionalized tiers feeding one national league above move the fewest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>Relegation % (share dropped)</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Spain Segunda Federacion ~30%; Spain Primera Federacion 25%; Italy Serie D ~22%; Germany 3. Liga 20%; Italy Serie B 20%</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>England League Two 8.3% (only 2 down); France National/Ligue tiers ~11% automatic floor</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Spain's RFEF tiers are the harshest (a quarter to a third relegated each year) due to funneling many regional groups into fewer national divisions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Most volatile pyramid</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>Spain (15% -&gt; 18% -&gt; 25% -&gt; 30% relegation gradient)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>England (stable 24-club tiers)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>Spain has by far the steepest relegation gradient down the tiers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>Most play-off dependent (top)</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>Germany (every tier 1/2/3 boundary = 2 auto + 1 relegation play-off)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>England (no relegation play-offs at all)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>Germany also has the most contentious structural step at tier 4 (5 champions, ~4 slots).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Least predictable</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Italy (ripescaggio / financial exclusions routinely override nominal numbers)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>England (transparent, rule-clean)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>Italian actual P/R frequently differs from the rules due to financial exclusions and 'fishing back'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Most administratively interventionist</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>France (DNCG can relegate clubs for finances)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>England (sporting results only)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>France is also mid-restructuring (18-club top flights; Ligue 3 arrives 2026-27).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Most stable single tier</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Premier League / Championship symmetry (15% &amp; 12.5% both ways)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>England.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Most extreme single tier</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Spain Segunda Federacion (~30% relegated / year)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>Spain.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Methodology, definitions &amp; cross-cutting notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>• Scope: most recent available league structures (2024-25 / 2025-26 seasons).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>• 'auto' = automatic on final league standings; 'PO' = via play-off; 'barrage' = French two-legged promotion/relegation play-off; 'playout' = Italian two-legged relegation play-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>• Promotion % = clubs promoted / clubs in division x 100. Relegation % = clubs relegated / clubs in division x 100. For regionalized tiers, percentages are computed per group where appropriate; national totals are given in the cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>• Ranges are given where the count depends on play-offs/barrages, licensing, reserve-team eligibility, financial exclusions, or ongoing league restructuring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>• Reserve/B-team rules: Spain - filiales capped at LaLiga2 and auto-relegated if parent drops into their tier; Germany - 'II' teams play up to 3. Liga but cannot be promoted above it (and are barred from the DFB-Pokal); Italy - reserve/U23 teams allowed only from Serie C down (never Serie A); France - reserves capped at National 2 (cannot reach tier 3+); England - no reserve teams in the senior pyramid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>• Conditional P/R: England - EFL ground-grading can deny a National League champion promotion; Italy - ripescaggio (financial exclusions refilled by readmitting/elevating clubs) routinely changes actual numbers; France - the DNCG can administratively relegate clubs for financial reasons (e.g. Bordeaux 2024-25, Lyon 2025 overturned on appeal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>• Regionalized tiers: Spain tiers 3-5, Germany tiers 4-5, Italy tiers 3-5, France tiers 4-5. Club counts and lower-tier relegation totals are set annually by regional federations and are therefore approximate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>• Upcoming changes flagged but outside the requested seasons: England Championship play-offs expand to 3rd-8th from 2026-27; France launches professional 'Ligue 3' (and renames National 2 -&gt; National 1, National 3 -&gt; National 2) from 2026-27; Germany's Regionalliga 4-division reform approved in principle, earliest 2028-29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>• Sourcing note: primarily official league/federation sites (Premier League/EFL, LaLiga/RFEF, Bundesliga.com/DFL/DFB, Lega Serie A/B/Pro/LND, LFP/FFF) and Wikipedia season/structure articles, cross-checked against reputable football media. Several official sites blocked direct fetching, so those figures were verified across multiple independent sources.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/football_promotion_relegation_top5.xlsx
+++ b/football_promotion_relegation_top5.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>~2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>~30%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>~8</t>
+          <t>~7</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>~7.6%</t>
+          <t>~7.4%</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>~11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>~10</t>
+          <t>~8 (variable)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>~20.8%</t>
+          <t>~16.7%</t>
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr">
@@ -2040,10 +2040,18 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Note: All figures triple-checked (3+ independent sources per number). France is mid-transition: Championnat National relegated 3 in 2024-25 (runs at 17 clubs in 2025-26) and National 2 relegations were reduced by an FFF transition decision, so its count is variable (~8).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A33:K33"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A31:K31"/>
